--- a/EU_Parlemeter_Data/Volume A/Sheet_Mappings.xlsx
+++ b/EU_Parlemeter_Data/Volume A/Sheet_Mappings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ashwin\Documents\GitHub\OpinionAndMedia_Data\EU_Parlemeter_Data\Volume A\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\Github\OpinionAndMedia_Data\EU_Parlemeter_Data\Volume A\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE9AF45-A2A4-403B-8387-6EA34EF7E0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD3B88E5-0209-4819-87BA-3F138AD8D83E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EP_Image" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="13">
   <si>
     <t>Year</t>
   </si>
@@ -33,32 +33,60 @@
     <t>Sheet</t>
   </si>
   <si>
-    <t>QP5</t>
-  </si>
-  <si>
-    <t>QB13</t>
-  </si>
-  <si>
-    <t>QP3</t>
-  </si>
-  <si>
-    <t>Q5</t>
-  </si>
-  <si>
-    <t>QA3</t>
-  </si>
-  <si>
-    <t>D78</t>
+    <t>T25</t>
+  </si>
+  <si>
+    <t>2021A</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>2022A</t>
+  </si>
+  <si>
+    <t>2023A</t>
+  </si>
+  <si>
+    <t>2022S</t>
+  </si>
+  <si>
+    <t>2025W</t>
+  </si>
+  <si>
+    <t>2021S</t>
+  </si>
+  <si>
+    <t>2025S</t>
+  </si>
+  <si>
+    <t>2025A</t>
+  </si>
+  <si>
+    <t>D1.1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -84,8 +112,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -366,10 +396,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -377,71 +407,144 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>2007</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2011</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>2010</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2012</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>2014</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2015</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2016</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>2017</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>2019</v>
       </c>
       <c r="B9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>2020</v>
+      </c>
+      <c r="B10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
         <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>